--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92649</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +774,209 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128226148</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90828</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>720</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>564861</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6683170</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128226159</v>
+      </c>
+      <c r="B4" t="n">
+        <v>86620</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>564873</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6683162</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86620</v>
+        <v>86621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,505 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128356312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92647</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>788</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564875</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683186</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128356264</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564849</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683242</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128356290</v>
+      </c>
+      <c r="B7" t="n">
+        <v>86623</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564879</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683157</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128356278</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86673</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>427</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Puderspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6683186</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128356243</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564861</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6683199</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1476,6 +1476,261 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128377519</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90835</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>720</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564873</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6683155</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 grupper</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128377526</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86624</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564873</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6683155</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92651</v>
+        <v>92659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90829</v>
+        <v>90835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86621</v>
+        <v>86624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92647</v>
+        <v>92652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128356264</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128356290</v>
       </c>
       <c r="B7" t="n">
-        <v>86623</v>
+        <v>86624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128356278</v>
       </c>
       <c r="B8" t="n">
-        <v>86673</v>
+        <v>86674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92659</v>
+        <v>92751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90835</v>
+        <v>90927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128356264</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128356290</v>
       </c>
       <c r="B7" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128356278</v>
       </c>
       <c r="B8" t="n">
-        <v>86674</v>
+        <v>86766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128377519</v>
       </c>
       <c r="B10" t="n">
-        <v>90835</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>128377526</v>
       </c>
       <c r="B11" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92751</v>
+        <v>92763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90927</v>
+        <v>90939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128356264</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128356290</v>
       </c>
       <c r="B7" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128356278</v>
       </c>
       <c r="B8" t="n">
-        <v>86766</v>
+        <v>86776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128377519</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>90939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>128377526</v>
       </c>
       <c r="B11" t="n">
-        <v>86716</v>
+        <v>86727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128356290</v>
       </c>
       <c r="B7" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128356278</v>
       </c>
       <c r="B8" t="n">
-        <v>86776</v>
+        <v>86778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128377519</v>
       </c>
       <c r="B10" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>128377526</v>
       </c>
       <c r="B11" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92765</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128377519</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128218806</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128226159</v>
       </c>
       <c r="B4" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128356312</v>
       </c>
       <c r="B5" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128356264</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128356290</v>
       </c>
       <c r="B7" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128356278</v>
       </c>
       <c r="B8" t="n">
-        <v>86778</v>
+        <v>86805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128356243</v>
       </c>
       <c r="B9" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128377519</v>
       </c>
       <c r="B10" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>128377526</v>
       </c>
       <c r="B11" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128218806</v>
+        <v>128356278</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1439</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sammetstaggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum martioflavum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564880</v>
+        <v>564877</v>
       </c>
       <c r="R2" t="n">
-        <v>6683183</v>
+        <v>6683186</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -779,11 +775,11 @@
         <v>128226148</v>
       </c>
       <c r="B3" t="n">
-        <v>90979</v>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,48 +878,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128226159</v>
+        <v>128377519</v>
       </c>
       <c r="B4" t="n">
-        <v>86760</v>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>564873</v>
       </c>
       <c r="R4" t="n">
-        <v>6683162</v>
+        <v>6683155</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,12 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 grupper</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -961,32 +965,53 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356312</v>
+        <v>128218823</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>93199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1010,17 +1035,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564875</v>
+        <v>564887</v>
       </c>
       <c r="R5" t="n">
-        <v>6683186</v>
+        <v>6683190</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,12 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,65 +1089,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356264</v>
+        <v>128226072</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>93199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564849</v>
+        <v>564879</v>
       </c>
       <c r="R6" t="n">
-        <v>6683242</v>
+        <v>6683150</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,12 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,60 +1186,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356290</v>
+        <v>128352972</v>
       </c>
       <c r="B7" t="n">
-        <v>86764</v>
+        <v>93199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564879</v>
+        <v>564884</v>
       </c>
       <c r="R7" t="n">
-        <v>6683157</v>
+        <v>6683186</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,44 +1283,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356278</v>
+        <v>128356312</v>
       </c>
       <c r="B8" t="n">
-        <v>86813</v>
+        <v>93199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>427</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,7 +1330,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564877</v>
+        <v>564875</v>
       </c>
       <c r="R8" t="n">
         <v>6683186</v>
@@ -1372,57 +1392,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356243</v>
+        <v>128377572</v>
       </c>
       <c r="B9" t="n">
-        <v>92443</v>
+        <v>93199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564861</v>
+        <v>564869</v>
       </c>
       <c r="R9" t="n">
-        <v>6683199</v>
+        <v>6683151</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1446,12 +1460,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,50 +1474,71 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128377519</v>
+        <v>128218806</v>
       </c>
       <c r="B10" t="n">
-        <v>90988</v>
+        <v>93206</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>1439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,17 +1547,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564873</v>
+        <v>564880</v>
       </c>
       <c r="R10" t="n">
-        <v>6683155</v>
+        <v>6683183</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,17 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 grupper</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1569,67 +1599,47 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128377526</v>
+        <v>128356271</v>
       </c>
       <c r="B11" t="n">
-        <v>86769</v>
+        <v>93206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>1439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Sammetstaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum martioflavum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1639,24 +1649,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564873</v>
+        <v>564871</v>
       </c>
       <c r="R11" t="n">
-        <v>6683155</v>
+        <v>6683153</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,42 +1702,1969 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128377584</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93206</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sammetstaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum martioflavum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Snell, K.A.Harrison &amp; H.A.C.Jacks.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564869</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6683151</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128226007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564898</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6683172</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128226159</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564873</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6683162</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128356290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564879</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6683157</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128377526</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564873</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6683155</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128218233</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564885</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6683146</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128218469</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564895</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6683160</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128218513</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>564889</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6683162</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128356354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>564887</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6683170</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128218080</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>564874</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6683145</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128218299</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>564885</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6683146</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128219072</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Södra Långviksgruvan, Södra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564841</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6683144</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128356232</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>564895</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6683164</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128356243</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>564861</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6683199</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128356254</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>564872</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6683137</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128218780</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>564904</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6683180</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128356306</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>564867</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6683149</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128356264</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>564849</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6683242</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128352866</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>564884</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6683186</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34928-2024 artfynd.xlsx
+++ b/artfynd/A 34928-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128377519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226072</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128352972</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356312</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128377572</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356271</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128377584</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2040,6 +2105,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128226159</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2137,6 +2207,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356290</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2266,6 +2341,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128377526</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2363,6 +2443,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218233</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2460,6 +2545,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218469</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2557,6 +2647,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218513</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2751,6 +2851,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218080</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218299</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2945,6 +3055,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128219072</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356232</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356243</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3263,6 +3388,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356254</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3360,6 +3490,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218780</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3466,6 +3601,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356306</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3568,6 +3708,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356264</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3665,8 +3810,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128352866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>